--- a/artfynd/A 15102-2025 artfynd.xlsx
+++ b/artfynd/A 15102-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121681479</v>
       </c>
       <c r="B2" t="n">
-        <v>57497</v>
+        <v>57503</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 15102-2025 artfynd.xlsx
+++ b/artfynd/A 15102-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121681479</v>
       </c>
       <c r="B2" t="n">
-        <v>57503</v>
+        <v>57506</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 15102-2025 artfynd.xlsx
+++ b/artfynd/A 15102-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121681479</v>
       </c>
       <c r="B2" t="n">
-        <v>57506</v>
+        <v>57507</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 15102-2025 artfynd.xlsx
+++ b/artfynd/A 15102-2025 artfynd.xlsx
@@ -678,16 +678,11 @@
         <v>121681479</v>
       </c>
       <c r="B2" t="n">
-        <v>57507</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -795,15 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121681781</v>
+        <v>121681721</v>
       </c>
       <c r="B3" t="n">
-        <v>58061</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58636</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -844,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577044</v>
+        <v>577226</v>
       </c>
       <c r="R3" t="n">
-        <v>6653903</v>
+        <v>6653689</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -874,22 +864,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,7 +899,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Indre Cepukaite</t>
+          <t>Diana Rubene</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -920,15 +910,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121681721</v>
+        <v>121681723</v>
       </c>
       <c r="B4" t="n">
-        <v>58061</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58636</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577226</v>
+        <v>577050</v>
       </c>
       <c r="R4" t="n">
-        <v>6653689</v>
+        <v>6653899</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -1004,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1014,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1045,15 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121681723</v>
+        <v>121681781</v>
       </c>
       <c r="B5" t="n">
-        <v>58061</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58636</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,10 +1074,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577050</v>
+        <v>577044</v>
       </c>
       <c r="R5" t="n">
-        <v>6653899</v>
+        <v>6653903</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1124,22 +1104,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,7 +1139,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Diana Rubene</t>
+          <t>Indre Cepukaite</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">

--- a/artfynd/A 15102-2025 artfynd.xlsx
+++ b/artfynd/A 15102-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
           <t>Rejlers - Sala till Avesta</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121681479</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -907,6 +917,11 @@
           <t>Rejlers - Sala till Avesta</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121681721</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1027,6 +1042,11 @@
           <t>Rejlers - Sala till Avesta</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121681723</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1147,8 +1167,19 @@
           <t>Rejlers - Sala till Avesta</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121681781</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>